--- a/output/horaires_shabbat.xlsx
+++ b/output/horaires_shabbat.xlsx
@@ -12760,36 +12760,36 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46066</v>
+        <v>46115</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>משפטים</t>
+          <t>פסח</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>משפטים</t>
+          <t>פסח</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12799,12 +12799,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -12819,45 +12819,49 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-04-08 00:39</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/horaires_shabbat.xlsx
+++ b/output/horaires_shabbat.xlsx
@@ -12760,36 +12760,36 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>פסח</t>
+          <t>שמיני</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>פסח</t>
+          <t>שמיני</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12814,54 +12814,50 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>19:25</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>לא</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>2026-04-08 00:39</t>
-        </is>
-      </c>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
